--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
@@ -19,14 +19,13 @@
     <sheet sheetId="13" name="Approvals" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="Skills" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="Hand-overs" state="visible" r:id="rId18"/>
-    <sheet sheetId="16" name="Adapted this cycle" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="1016">
   <si>
     <t>Metric</t>
   </si>
@@ -169,7 +168,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T16:15:57.789Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T16:44:47.269Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -2271,6 +2270,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>Low</t>
+  </si>
+  <si>
     <t>Non-functional</t>
   </si>
   <si>
@@ -2298,9 +2300,6 @@
     <t>Confirm the behaviour "Templates support required locale and accessibility standards." (no executable template in the catalogue - manual verification).</t>
   </si>
   <si>
-    <t>Low</t>
-  </si>
-  <si>
     <t>AQPI-24, REQ-082, BR-082</t>
   </si>
   <si>
@@ -2814,7 +2813,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-11T16:15:59.183Z</t>
+    <t>2026-10-11T16:44:49.001Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -2826,7 +2825,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-11T16:15:59.207Z</t>
+    <t>2026-10-11T16:44:49.056Z</t>
   </si>
   <si>
     <t>23 requirements, 0 test cases, 0 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -3094,15 +3093,6 @@
   </si>
   <si>
     <t>cycleReport: delivered; comparison: delivered; testCaseExport: delivered</t>
-  </si>
-  <si>
-    <t>Lesson applied</t>
-  </si>
-  <si>
-    <t>risk-based priority</t>
-  </si>
-  <si>
-    <t>REQ-023 tested at High priority: defect history - DEF-009 on story AQPI-4</t>
   </si>
 </sst>
 </file>
@@ -4724,7 +4714,7 @@
         <v>134</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>897</v>
@@ -4754,7 +4744,7 @@
         <v>263</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>707</v>
@@ -4795,16 +4785,16 @@
         <v>408</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>134</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>900</v>
@@ -4843,7 +4833,7 @@
         <v>134</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>901</v>
@@ -4882,7 +4872,7 @@
         <v>134</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>902</v>
@@ -4921,7 +4911,7 @@
         <v>134</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>903</v>
@@ -5471,37 +5461,6 @@
       </c>
       <c r="E11" s="2" t="s">
         <v>1015</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1018</v>
       </c>
     </row>
   </sheetData>
@@ -11461,19 +11420,19 @@
         <v>163</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>690</v>
@@ -11487,7 +11446,7 @@
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>707</v>
@@ -11517,7 +11476,7 @@
         <v>687</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>689</v>
@@ -11534,13 +11493,13 @@
     </row>
     <row r="11" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>738</v>
@@ -11555,19 +11514,19 @@
         <v>407</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>751</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>690</v>
@@ -11602,19 +11561,19 @@
         <v>481</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>755</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>690</v>
@@ -11649,19 +11608,19 @@
         <v>498</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>759</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>690</v>
@@ -11696,19 +11655,19 @@
         <v>515</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>763</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>690</v>
@@ -11778,7 +11737,7 @@
         <v>769</v>
       </c>
       <c r="E2" s="2">
-        <v>1108</v>
+        <v>1184</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -11797,7 +11756,7 @@
         <v>769</v>
       </c>
       <c r="E3" s="2">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -11816,7 +11775,7 @@
         <v>769</v>
       </c>
       <c r="E4" s="2">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11835,7 +11794,7 @@
         <v>769</v>
       </c>
       <c r="E5" s="2">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -11854,7 +11813,7 @@
         <v>769</v>
       </c>
       <c r="E6" s="2">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -11873,7 +11832,7 @@
         <v>769</v>
       </c>
       <c r="E7" s="2">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -11892,7 +11851,7 @@
         <v>769</v>
       </c>
       <c r="E8" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -11920,7 +11879,7 @@
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>261</v>
@@ -11932,20 +11891,20 @@
         <v>769</v>
       </c>
       <c r="E10" s="2">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>406</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>770</v>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="1016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="1018">
   <si>
     <t>Metric</t>
   </si>
@@ -168,7 +168,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T16:44:47.269Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T17:07:17.764Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -2408,13 +2408,13 @@
     <t>Minor</t>
   </si>
   <si>
-    <t>not raised in Jira</t>
-  </si>
-  <si>
-    <t>Code implements AQPI-8 (4 acceptance criteria)</t>
-  </si>
-  <si>
-    <t>No code in demo/hotel-booking-platform mentions AQPI-8</t>
+    <t>not raised in Jira; linked to AQPI-8 in the platform</t>
+  </si>
+  <si>
+    <t>The code implements AQPI-8 4.2 Sort and filter hotel results (4 acceptance criteria)</t>
+  </si>
+  <si>
+    <t>No code in sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) mentions AQPI-8</t>
   </si>
   <si>
     <t>implemented in code, not yet verified by a test of this testing type</t>
@@ -2426,10 +2426,13 @@
     <t>AQPI-13 5.3 Explain and control personalization: asked for in Jira but not implemented in the code</t>
   </si>
   <si>
-    <t>Code implements AQPI-13 (3 acceptance criteria)</t>
-  </si>
-  <si>
-    <t>No code in demo/hotel-booking-platform mentions AQPI-13</t>
+    <t>not raised in Jira; linked to AQPI-13 in the platform</t>
+  </si>
+  <si>
+    <t>The code implements AQPI-13 5.3 Explain and control personalization (3 acceptance criteria)</t>
+  </si>
+  <si>
+    <t>No code in sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) mentions AQPI-13</t>
   </si>
   <si>
     <t>DEF-003</t>
@@ -2438,10 +2441,13 @@
     <t>AQPI-22 7.4 Show booking outcome: asked for in Jira but not implemented in the code</t>
   </si>
   <si>
-    <t>Code implements AQPI-22 (3 acceptance criteria)</t>
-  </si>
-  <si>
-    <t>No code in demo/hotel-booking-platform mentions AQPI-22</t>
+    <t>not raised in Jira; linked to AQPI-22 in the platform</t>
+  </si>
+  <si>
+    <t>The code implements AQPI-22 7.4 Show booking outcome (3 acceptance criteria)</t>
+  </si>
+  <si>
+    <t>No code in sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) mentions AQPI-22</t>
   </si>
   <si>
     <t>First seen</t>
@@ -2813,7 +2819,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-11T16:44:49.001Z</t>
+    <t>2026-10-11T17:07:19.057Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -2825,7 +2831,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-11T16:44:49.056Z</t>
+    <t>2026-10-11T17:07:19.080Z</t>
   </si>
   <si>
     <t>23 requirements, 0 test cases, 0 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -3695,19 +3701,19 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
@@ -3736,16 +3742,16 @@
         <v>575</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -3766,7 +3772,7 @@
         <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3774,16 +3780,16 @@
         <v>531</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>852</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
@@ -3804,7 +3810,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3812,16 +3818,16 @@
         <v>558</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>852</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -3842,7 +3848,7 @@
         <v>69</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3850,16 +3856,16 @@
         <v>546</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>852</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -3880,7 +3886,7 @@
         <v>69</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3888,16 +3894,16 @@
         <v>587</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>852</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -3918,24 +3924,24 @@
         <v>69</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -3956,7 +3962,7 @@
         <v>69</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3964,16 +3970,16 @@
         <v>399</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>852</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -3994,7 +4000,7 @@
         <v>69</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4002,16 +4008,16 @@
         <v>418</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>852</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -4032,7 +4038,7 @@
         <v>69</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4040,16 +4046,16 @@
         <v>439</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>852</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -4070,7 +4076,7 @@
         <v>69</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4078,16 +4084,16 @@
         <v>610</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>852</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -4108,7 +4114,7 @@
         <v>69</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4116,16 +4122,16 @@
         <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
@@ -4146,7 +4152,7 @@
         <v>69</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4154,16 +4160,16 @@
         <v>150</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -4184,7 +4190,7 @@
         <v>69</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4192,16 +4198,16 @@
         <v>250</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -4222,7 +4228,7 @@
         <v>69</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4230,16 +4236,16 @@
         <v>472</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -4260,7 +4266,7 @@
         <v>69</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4268,16 +4274,16 @@
         <v>497</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -4298,7 +4304,7 @@
         <v>69</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4306,16 +4312,16 @@
         <v>514</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -4336,7 +4342,7 @@
         <v>69</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -4371,13 +4377,13 @@
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>666</v>
@@ -4386,19 +4392,19 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>765</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>775</v>
@@ -4430,10 +4436,10 @@
         <v>689</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>769</v>
@@ -4471,10 +4477,10 @@
         <v>689</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>769</v>
@@ -4512,10 +4518,10 @@
         <v>689</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>769</v>
@@ -4553,10 +4559,10 @@
         <v>689</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>769</v>
@@ -4594,10 +4600,10 @@
         <v>689</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>769</v>
@@ -4635,10 +4641,10 @@
         <v>689</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>769</v>
@@ -4676,10 +4682,10 @@
         <v>689</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>769</v>
@@ -4717,7 +4723,7 @@
         <v>745</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
@@ -4756,10 +4762,10 @@
         <v>689</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>769</v>
@@ -4797,7 +4803,7 @@
         <v>745</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
@@ -4836,7 +4842,7 @@
         <v>745</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
@@ -4875,7 +4881,7 @@
         <v>745</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
@@ -4914,7 +4920,7 @@
         <v>745</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -4951,40 +4957,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>767</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
   </sheetData>
@@ -5007,53 +5013,53 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
   </sheetData>
@@ -5076,189 +5082,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
   </sheetData>
@@ -5281,186 +5287,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
   </sheetData>
@@ -11737,7 +11743,7 @@
         <v>769</v>
       </c>
       <c r="E2" s="2">
-        <v>1184</v>
+        <v>1106</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -11756,7 +11762,7 @@
         <v>769</v>
       </c>
       <c r="E3" s="2">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -11775,7 +11781,7 @@
         <v>769</v>
       </c>
       <c r="E4" s="2">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11794,7 +11800,7 @@
         <v>769</v>
       </c>
       <c r="E5" s="2">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -11813,7 +11819,7 @@
         <v>769</v>
       </c>
       <c r="E6" s="2">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -11832,7 +11838,7 @@
         <v>769</v>
       </c>
       <c r="E7" s="2">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -11851,7 +11857,7 @@
         <v>769</v>
       </c>
       <c r="E8" s="2">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -11891,7 +11897,7 @@
         <v>769</v>
       </c>
       <c r="E10" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -12097,15 +12103,15 @@
         <v>640</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>790</v>
@@ -12117,10 +12123,10 @@
     </row>
     <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>786</v>
@@ -12129,15 +12135,15 @@
         <v>653</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>790</v>
@@ -12179,10 +12185,10 @@
         <v>764</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>765</v>
@@ -12191,7 +12197,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -12218,16 +12224,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>689</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -12256,7 +12262,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12279,7 +12285,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12302,7 +12308,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12325,7 +12331,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12348,7 +12354,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12371,7 +12377,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12394,7 +12400,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12417,7 +12423,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12440,7 +12446,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12463,7 +12469,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12486,7 +12492,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12509,7 +12515,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12532,7 +12538,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12555,7 +12561,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12578,7 +12584,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12601,7 +12607,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12624,7 +12630,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12647,7 +12653,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12670,7 +12676,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12693,7 +12699,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12716,7 +12722,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12739,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12762,7 +12768,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12785,7 +12791,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12808,7 +12814,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12831,7 +12837,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12854,7 +12860,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12877,7 +12883,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12900,7 +12906,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12923,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12946,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12969,7 +12975,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12992,7 +12998,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13015,7 +13021,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13038,7 +13044,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13061,7 +13067,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13084,7 +13090,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13107,7 +13113,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13130,7 +13136,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13153,7 +13159,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13176,7 +13182,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13199,7 +13205,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13222,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13245,7 +13251,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13268,7 +13274,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13291,7 +13297,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13314,7 +13320,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13337,7 +13343,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13360,7 +13366,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13383,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13406,7 +13412,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13429,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13452,7 +13458,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13475,7 +13481,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13498,7 +13504,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13521,7 +13527,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13544,7 +13550,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13567,7 +13573,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13590,7 +13596,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13613,7 +13619,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13636,7 +13642,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13659,7 +13665,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13682,7 +13688,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13705,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13728,7 +13734,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13751,7 +13757,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13774,7 +13780,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13797,7 +13803,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13820,7 +13826,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13843,7 +13849,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13866,7 +13872,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13889,7 +13895,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13912,7 +13918,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13935,7 +13941,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13958,7 +13964,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13981,7 +13987,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14004,7 +14010,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14027,7 +14033,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14050,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14073,7 +14079,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14096,7 +14102,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14119,7 +14125,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14142,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14165,7 +14171,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14188,7 +14194,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14211,7 +14217,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14234,7 +14240,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14257,7 +14263,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14280,7 +14286,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14303,7 +14309,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14326,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14349,7 +14355,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14372,7 +14378,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14395,7 +14401,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14418,7 +14424,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14441,7 +14447,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14464,7 +14470,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14487,7 +14493,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14510,7 +14516,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14533,7 +14539,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14556,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14579,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14602,7 +14608,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14625,7 +14631,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14648,7 +14654,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14671,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14694,7 +14700,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14717,7 +14723,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14740,7 +14746,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14763,7 +14769,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14786,7 +14792,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14809,7 +14815,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14832,7 +14838,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14855,7 +14861,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14878,7 +14884,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14901,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14924,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14947,7 +14953,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14970,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14993,7 +14999,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15016,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15039,7 +15045,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15062,7 +15068,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15085,7 +15091,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15108,7 +15114,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15131,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15154,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15177,7 +15183,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="130" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15200,7 +15206,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="131" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15223,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="132" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15246,7 +15252,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="133" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15269,7 +15275,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="134" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15292,7 +15298,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="135" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15315,7 +15321,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="136" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15338,7 +15344,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="137" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15361,7 +15367,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="138" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15384,7 +15390,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="139" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15407,7 +15413,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -15429,13 +15435,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -15443,212 +15449,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>692</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>714</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
@@ -87,7 +87,7 @@
     <t>{"functional":8,"eqe":13,"automation":8,"regression":13,"non-functional":5}</t>
   </si>
   <si>
-    <t>Scripts</t>
+    <t>Automation scripts</t>
   </si>
   <si>
     <t>Executed (real)</t>
@@ -168,7 +168,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T17:07:17.764Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-12T01:35:37.047Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -2819,7 +2819,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-11T17:07:19.057Z</t>
+    <t>2026-10-12T01:35:38.475Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -2831,7 +2831,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-11T17:07:19.080Z</t>
+    <t>2026-10-12T01:35:38.498Z</t>
   </si>
   <si>
     <t>23 requirements, 0 test cases, 0 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -11743,7 +11743,7 @@
         <v>769</v>
       </c>
       <c r="E2" s="2">
-        <v>1106</v>
+        <v>1718</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -11762,7 +11762,7 @@
         <v>769</v>
       </c>
       <c r="E3" s="2">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -11781,7 +11781,7 @@
         <v>769</v>
       </c>
       <c r="E4" s="2">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11800,7 +11800,7 @@
         <v>769</v>
       </c>
       <c r="E5" s="2">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -11819,7 +11819,7 @@
         <v>769</v>
       </c>
       <c r="E6" s="2">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -11838,7 +11838,7 @@
         <v>769</v>
       </c>
       <c r="E7" s="2">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -11857,7 +11857,7 @@
         <v>769</v>
       </c>
       <c r="E8" s="2">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -11897,7 +11897,7 @@
         <v>769</v>
       </c>
       <c r="E10" s="2">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="1067">
   <si>
     <t>Metric</t>
   </si>
@@ -78,13 +78,13 @@
     <t>Test cases by type</t>
   </si>
   <si>
-    <t>{"functional":8,"non-functional":5}</t>
+    <t>{"functional":13,"non-functional":5}</t>
   </si>
   <si>
     <t>Test cases by label</t>
   </si>
   <si>
-    <t>{"functional":8,"eqe":13,"automation":8,"regression":13,"non-functional":5}</t>
+    <t>{"functional":13,"eqe":18,"automation":13,"regression":13,"non-functional":5}</t>
   </si>
   <si>
     <t>Automation scripts</t>
@@ -117,7 +117,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) · EQE (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 20 new). 13 test cases are designed, 8 of them automated in 7 Playwright scripts. Execution ran 8 automated cases for real: 8 passed and 0 failed (pass rate 100%). 3 defect(s) were raised from real failures: DEF-001 AQPI-8 4.2 Sort and filter hotel results: asked for in Jira but not implemented in the code; DEF-002 AQPI-13 5.3 Explain and control personalization: asked for in Jira but not implemented in the code; DEF-003 AQPI-22 7.4 Show booking outcome: asked for in Jira but not implemented in the code.</t>
+    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) · EQE (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 20 new). 18 test cases are designed, 13 of them automated in 12 Playwright scripts. Execution ran 13 automated cases for real: 13 passed and 0 failed (pass rate 100%). No defects were raised.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -162,13 +162,13 @@
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44)</t>
+    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-12T01:35:37.047Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) at 2026-10-12T02:10:38.267Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -2339,6 +2339,125 @@
     <t>AQPI-31, REQ-108, BR-108</t>
   </si>
   <si>
+    <t>TC-F-009</t>
+  </si>
+  <si>
+    <t>Guest books a flexible room, then cancels it free of charge more than 48 hours before check-in</t>
+  </si>
+  <si>
+    <t>Verify the release 2.0 cancellation journey across search, cart, reservation and payment: the booking ends cancelled and the payment hold is voided.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search NYC
+2. Book a FLEX rate 30 days ahead
+3. Cancel the reservation
+4. View the reservation</t>
+  </si>
+  <si>
+    <t>selection.ratePlanCode=FLEX; every other booking attribute from the hotel data dictionary examples</t>
+  </si>
+  <si>
+    <t>Booking HTTP 201 CONFIRMED; cancel HTTP 200 CANCELLED with payment VOIDED; the reservation stays CANCELLED</t>
+  </si>
+  <si>
+    <t>functional, eqe, automation</t>
+  </si>
+  <si>
+    <t>AQPI-36, REQ-121, BR-121</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>TC-F-010</t>
+  </si>
+  <si>
+    <t>Guest books, cancels and receives exactly one confirmation and one cancellation e-mail</t>
+  </si>
+  <si>
+    <t>Verify the release 2.0 cancellation journey across reservation and notification: the guest is told once about the booking and once about the cancellation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a FLEX rate
+2. Open the confirmation e-mail
+3. Cancel the reservation
+4. List its messages as support</t>
+  </si>
+  <si>
+    <t>Booking CONFIRMED with its e-mail; cancel HTTP 200 CANCELLED; exactly one CONFIRMATION and one CANCELLATION message</t>
+  </si>
+  <si>
+    <t>AQPI-37, REQ-126, BR-126</t>
+  </si>
+  <si>
+    <t>TC-F-011</t>
+  </si>
+  <si>
+    <t>Guest sorts the results by lowest price, then books a room from the sorted results</t>
+  </si>
+  <si>
+    <t>Verify the sort-and-book journey across the search, cart and reservation services.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search NYC
+2. Sort the results by lowest price
+3. Create a cart for a hotel in the results
+4. Submit the reservation</t>
+  </si>
+  <si>
+    <t>Bookable results in non-decreasing price order; the chosen hotel is in them; HTTP 201 CONFIRMED</t>
+  </si>
+  <si>
+    <t>AQPI-8, REQ-130, BR-130</t>
+  </si>
+  <si>
+    <t>TC-F-012</t>
+  </si>
+  <si>
+    <t>Guest is shown extras, declines them all and books the room only</t>
+  </si>
+  <si>
+    <t>Verify the offers never block the journey: search, offers, cart without extras, reservation and confirmation e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search NYC
+2. Get recommended extras
+3. Create a cart without any extra
+4. Submit the reservation
+5. Open the confirmation e-mail</t>
+  </si>
+  <si>
+    <t>Extras offered; HTTP 201 CONFIRMED with optional extras 0; confirmation e-mail carries the confirmation number</t>
+  </si>
+  <si>
+    <t>AQPI-13, REQ-134, BR-134</t>
+  </si>
+  <si>
+    <t>TC-F-013</t>
+  </si>
+  <si>
+    <t>Guest books a room with breakfast and sees the full booking outcome, matching the confirmation e-mail</t>
+  </si>
+  <si>
+    <t>Verify the guest sees a clear success outcome at the end of the journey, consistent with the e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search NYC
+2. Create a cart with breakfast
+3. Submit the reservation
+4. Read the booking outcome
+5. Open the confirmation e-mail</t>
+  </si>
+  <si>
+    <t>extras.code=BREAKFAST; extras.quantity=1; every other booking attribute from the hotel data dictionary examples</t>
+  </si>
+  <si>
+    <t>Outcome shows confirmation number, hotel, stay dates, breakfast and total; the e-mail has the same confirmation number</t>
+  </si>
+  <si>
+    <t>AQPI-22, REQ-136, BR-136</t>
+  </si>
+  <si>
     <t>Case</t>
   </si>
   <si>
@@ -2399,25 +2518,31 @@
     <t>AI likely cause</t>
   </si>
   <si>
+    <t>First seen</t>
+  </si>
+  <si>
+    <t>Retested in</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
     <t>DEF-001</t>
   </si>
   <si>
     <t>AQPI-8 4.2 Sort and filter hotel results: asked for in Jira but not implemented in the code</t>
   </si>
   <si>
-    <t>Minor</t>
-  </si>
-  <si>
-    <t>not raised in Jira; linked to AQPI-8 in the platform</t>
-  </si>
-  <si>
-    <t>The code implements AQPI-8 4.2 Sort and filter hotel results (4 acceptance criteria)</t>
-  </si>
-  <si>
-    <t>No code in sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) mentions AQPI-8</t>
-  </si>
-  <si>
-    <t>implemented in code, not yet verified by a test of this testing type</t>
+    <t>CYC-1</t>
+  </si>
+  <si>
+    <t>CYC-4</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>AQPI-8 is implemented in build demo/hotel-booking-platform-v2; 1 test(s) of the picked-up gap passed in CYC-4, so DEF-001 (gap from CYC-1) is closed.</t>
   </si>
   <si>
     <t>DEF-002</t>
@@ -2426,13 +2551,7 @@
     <t>AQPI-13 5.3 Explain and control personalization: asked for in Jira but not implemented in the code</t>
   </si>
   <si>
-    <t>not raised in Jira; linked to AQPI-13 in the platform</t>
-  </si>
-  <si>
-    <t>The code implements AQPI-13 5.3 Explain and control personalization (3 acceptance criteria)</t>
-  </si>
-  <si>
-    <t>No code in sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) mentions AQPI-13</t>
+    <t>AQPI-13 is implemented in build demo/hotel-booking-platform-v2; 1 test(s) of the picked-up gap passed in CYC-4, so DEF-002 (gap from CYC-1) is closed.</t>
   </si>
   <si>
     <t>DEF-003</t>
@@ -2441,22 +2560,7 @@
     <t>AQPI-22 7.4 Show booking outcome: asked for in Jira but not implemented in the code</t>
   </si>
   <si>
-    <t>not raised in Jira; linked to AQPI-22 in the platform</t>
-  </si>
-  <si>
-    <t>The code implements AQPI-22 7.4 Show booking outcome (3 acceptance criteria)</t>
-  </si>
-  <si>
-    <t>No code in sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) mentions AQPI-22</t>
-  </si>
-  <si>
-    <t>First seen</t>
-  </si>
-  <si>
-    <t>Retested in</t>
-  </si>
-  <si>
-    <t>Certification</t>
+    <t>AQPI-22 is implemented in build demo/hotel-booking-platform-v2; 1 test(s) of the picked-up gap passed in CYC-4, so DEF-003 (gap from CYC-1) is closed.</t>
   </si>
   <si>
     <t>Text</t>
@@ -2552,13 +2656,16 @@
     <t>FLEX = pay at hotel with a card guarantee; SAVER = prepaid, non-refundable</t>
   </si>
   <si>
+    <t>TC-F-001, TC-F-002, TC-F-009, TC-F-010</t>
+  </si>
+  <si>
     <t>extras.code</t>
   </si>
   <si>
     <t>Optional ancillary added to the cart (empty = none)</t>
   </si>
   <si>
-    <t>TC-F-001, TC-F-004, TC-F-008</t>
+    <t>TC-F-001, TC-F-004, TC-F-008, TC-F-013</t>
   </si>
   <si>
     <t>extras.quantity</t>
@@ -2630,6 +2737,9 @@
     <t>10.4 Cancel a reservation free of charge</t>
   </si>
   <si>
+    <t>verified</t>
+  </si>
+  <si>
     <t>AQPI-23</t>
   </si>
   <si>
@@ -2660,21 +2770,33 @@
     <t>[Initiative] Intelligent Hotel Shopping and Reservation Experience</t>
   </si>
   <si>
-    <t>verified</t>
-  </si>
-  <si>
     <t>AQPI-2</t>
   </si>
   <si>
     <t>3.2 Validate occupancy and stay criteria</t>
   </si>
   <si>
+    <t>AQPI-6</t>
+  </si>
+  <si>
+    <t>4.2 Sort and filter hotel results</t>
+  </si>
+  <si>
     <t>AQPI-10</t>
   </si>
   <si>
     <t>5.2 Display ancillary offers</t>
   </si>
   <si>
+    <t>5.3 Explain and control personalization</t>
+  </si>
+  <si>
+    <t>AQPI-18</t>
+  </si>
+  <si>
+    <t>7.4 Show booking outcome</t>
+  </si>
+  <si>
     <t>AQPI-27</t>
   </si>
   <si>
@@ -2765,6 +2887,36 @@
     <t>TD-N-005</t>
   </si>
   <si>
+    <t>TD-F-009</t>
+  </si>
+  <si>
+    <t>br-121-free-cancellation.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-010</t>
+  </si>
+  <si>
+    <t>br-126-cancellation-email.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-011</t>
+  </si>
+  <si>
+    <t>br-130-result-sorting.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-012</t>
+  </si>
+  <si>
+    <t>br-134-proceed-without-offers.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-013</t>
+  </si>
+  <si>
+    <t>br-136-booking-outcome.spec.js</t>
+  </si>
+  <si>
     <t>Call</t>
   </si>
   <si>
@@ -2819,7 +2971,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-12T01:35:38.475Z</t>
+    <t>2026-10-12T02:10:39.649Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -2831,10 +2983,10 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-12T01:35:38.498Z</t>
-  </si>
-  <si>
-    <t>23 requirements, 0 test cases, 0 scripts merged: BL-1 v1 -&gt; v2</t>
+    <t>2026-10-12T02:10:39.674Z</t>
+  </si>
+  <si>
+    <t>23 requirements, 5 test cases, 5 scripts merged: BL-1 v1 -&gt; v2</t>
   </si>
   <si>
     <t>Skill id</t>
@@ -2936,6 +3088,18 @@
     <t>input-review.md</t>
   </si>
   <si>
+    <t>release-criteria</t>
+  </si>
+  <si>
+    <t>Release criteria (Go / Conditional go / No-go)</t>
+  </si>
+  <si>
+    <t>The parameters the cycle report applies to recommend Go, Conditional go or No-go. Edit this file, or upload a replacement, to change them without a code change.</t>
+  </si>
+  <si>
+    <t>release-criteria.md</t>
+  </si>
+  <si>
     <t>test-case-authoring</t>
   </si>
   <si>
@@ -3095,10 +3259,10 @@
     <t>Cycle report agent</t>
   </si>
   <si>
-    <t>cycle-report, test-case-authoring, testing-eqe, traceability-handover</t>
-  </si>
-  <si>
-    <t>cycleReport: delivered; comparison: delivered; testCaseExport: delivered</t>
+    <t>cycle-report, release-criteria, test-case-authoring, testing-eqe, traceability-handover</t>
+  </si>
+  <si>
+    <t>cycleReport: delivered; comparison: delivered; releaseDecision: delivered; testCaseExport: delivered</t>
   </si>
 </sst>
 </file>
@@ -3118,7 +3282,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3135,6 +3299,11 @@
         <fgColor rgb="FFF1F3F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF3E4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -3148,13 +3317,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3572,7 +3744,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3596,7 +3768,7 @@
         <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3604,7 +3776,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3612,7 +3784,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3644,7 +3816,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3652,7 +3824,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>5.1</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3687,7 +3859,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="11" customWidth="1"/>
@@ -3701,19 +3873,19 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>848</v>
+        <v>878</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>849</v>
+        <v>879</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>850</v>
+        <v>880</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>851</v>
+        <v>881</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>852</v>
+        <v>882</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
@@ -3742,16 +3914,16 @@
         <v>575</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>853</v>
+        <v>883</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -3772,7 +3944,7 @@
         <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3780,16 +3952,16 @@
         <v>531</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>857</v>
+        <v>887</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
@@ -3810,7 +3982,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3818,16 +3990,16 @@
         <v>558</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>858</v>
+        <v>888</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -3848,7 +4020,7 @@
         <v>69</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3856,16 +4028,16 @@
         <v>546</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>859</v>
+        <v>889</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -3886,7 +4058,7 @@
         <v>69</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3894,28 +4066,28 @@
         <v>587</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
@@ -3924,24 +4096,24 @@
         <v>69</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>808</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>861</v>
+        <v>892</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>853</v>
+        <v>883</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>862</v>
+        <v>893</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -3962,7 +4134,7 @@
         <v>69</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3970,16 +4142,16 @@
         <v>399</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>861</v>
+        <v>892</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>863</v>
+        <v>894</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -4000,7 +4172,7 @@
         <v>69</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>864</v>
+        <v>895</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4008,16 +4180,16 @@
         <v>418</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>861</v>
+        <v>892</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>865</v>
+        <v>896</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -4038,7 +4210,7 @@
         <v>69</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4046,16 +4218,16 @@
         <v>439</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>861</v>
+        <v>892</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>866</v>
+        <v>897</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -4076,7 +4248,7 @@
         <v>69</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4084,28 +4256,28 @@
         <v>610</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>861</v>
+        <v>892</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>867</v>
+        <v>898</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
@@ -4114,7 +4286,7 @@
         <v>69</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>808</v>
+        <v>891</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4122,16 +4294,16 @@
         <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>868</v>
+        <v>899</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>869</v>
+        <v>900</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>870</v>
+        <v>901</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
@@ -4152,7 +4324,7 @@
         <v>69</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>871</v>
+        <v>891</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4160,16 +4332,16 @@
         <v>150</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>869</v>
+        <v>900</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>872</v>
+        <v>902</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>873</v>
+        <v>903</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -4190,24 +4362,24 @@
         <v>69</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>864</v>
+        <v>895</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>250</v>
+        <v>623</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>869</v>
+        <v>900</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>874</v>
+        <v>904</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>875</v>
+        <v>905</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -4228,24 +4400,24 @@
         <v>69</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>871</v>
+        <v>891</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>472</v>
+        <v>250</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>869</v>
+        <v>900</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>876</v>
+        <v>906</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>877</v>
+        <v>907</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -4254,10 +4426,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2">
         <v>0</v>
@@ -4266,24 +4438,24 @@
         <v>69</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>497</v>
+        <v>640</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>869</v>
+        <v>900</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>876</v>
+        <v>906</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>878</v>
+        <v>908</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -4292,10 +4464,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2">
         <v>0</v>
@@ -4304,45 +4476,159 @@
         <v>69</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>864</v>
+      <c r="B20" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -4353,7 +4639,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -4377,13 +4663,13 @@
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>880</v>
+        <v>915</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>881</v>
+        <v>916</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>666</v>
@@ -4392,22 +4678,22 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>882</v>
+        <v>917</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>883</v>
+        <v>918</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>884</v>
+        <v>919</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>765</v>
+        <v>799</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>885</v>
+        <v>920</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>775</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4436,13 +4722,13 @@
         <v>689</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>886</v>
+        <v>921</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>887</v>
+        <v>922</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>69</v>
@@ -4477,13 +4763,13 @@
         <v>689</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>888</v>
+        <v>923</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>887</v>
+        <v>922</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>69</v>
@@ -4518,13 +4804,13 @@
         <v>689</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>890</v>
+        <v>925</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>69</v>
@@ -4559,13 +4845,13 @@
         <v>689</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>891</v>
+        <v>926</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>892</v>
+        <v>927</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>69</v>
@@ -4600,13 +4886,13 @@
         <v>689</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>893</v>
+        <v>928</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>894</v>
+        <v>929</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>69</v>
@@ -4641,13 +4927,13 @@
         <v>689</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>896</v>
+        <v>931</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>69</v>
@@ -4682,13 +4968,13 @@
         <v>689</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>897</v>
+        <v>932</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>898</v>
+        <v>933</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>69</v>
@@ -4723,11 +5009,11 @@
         <v>745</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>899</v>
+        <v>934</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>69</v>
@@ -4762,13 +5048,13 @@
         <v>689</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>900</v>
+        <v>935</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>901</v>
+        <v>936</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>69</v>
@@ -4803,11 +5089,11 @@
         <v>745</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>902</v>
+        <v>937</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>69</v>
@@ -4842,11 +5128,11 @@
         <v>745</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>903</v>
+        <v>938</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>69</v>
@@ -4881,11 +5167,11 @@
         <v>745</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>904</v>
+        <v>939</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>69</v>
@@ -4920,16 +5206,221 @@
         <v>745</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>905</v>
+        <v>940</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="M14" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M19" s="2" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4957,40 +5448,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>906</v>
+        <v>951</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>907</v>
+        <v>952</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>908</v>
+        <v>953</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>909</v>
+        <v>954</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>910</v>
+        <v>955</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>911</v>
+        <v>956</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>912</v>
+        <v>957</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>913</v>
+        <v>958</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>914</v>
+        <v>959</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>915</v>
+        <v>960</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>767</v>
+        <v>801</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>916</v>
+        <v>961</v>
       </c>
     </row>
   </sheetData>
@@ -5013,53 +5504,53 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>917</v>
+        <v>962</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>918</v>
+        <v>963</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>919</v>
+        <v>964</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>910</v>
+        <v>955</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>920</v>
+        <v>965</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>921</v>
+        <v>966</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>922</v>
+        <v>967</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>923</v>
+        <v>968</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>924</v>
+        <v>969</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>925</v>
+        <v>970</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>926</v>
+        <v>971</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>922</v>
+        <v>967</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>927</v>
+        <v>972</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>928</v>
+        <v>973</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>929</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -5070,7 +5561,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -5082,189 +5573,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>930</v>
+        <v>975</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>811</v>
+        <v>840</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>931</v>
+        <v>976</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>932</v>
+        <v>977</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>933</v>
+        <v>978</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>934</v>
+        <v>979</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>935</v>
+        <v>980</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>936</v>
+        <v>981</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>937</v>
+        <v>982</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>938</v>
+        <v>983</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>939</v>
+        <v>984</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>940</v>
+        <v>985</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>941</v>
+        <v>986</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>942</v>
+        <v>987</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>943</v>
+        <v>988</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>944</v>
+        <v>989</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>945</v>
+        <v>990</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>946</v>
+        <v>991</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>947</v>
+        <v>992</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>948</v>
+        <v>993</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>949</v>
+        <v>994</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>950</v>
+        <v>995</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>951</v>
+        <v>996</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>952</v>
+        <v>997</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>953</v>
+        <v>998</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>954</v>
+        <v>999</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>955</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>956</v>
+        <v>1001</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>957</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>958</v>
+        <v>1003</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>959</v>
+        <v>1004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>960</v>
+        <v>1005</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>961</v>
+        <v>1006</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>962</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>963</v>
+        <v>1008</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>964</v>
+        <v>1009</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>965</v>
+        <v>1010</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>966</v>
+        <v>986</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>967</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>968</v>
+        <v>1012</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>969</v>
+        <v>1013</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>970</v>
+        <v>1014</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>971</v>
+        <v>1015</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>972</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>973</v>
+        <v>1017</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>974</v>
+        <v>1018</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>975</v>
+        <v>1019</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>976</v>
+        <v>1020</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>977</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>978</v>
+        <v>1022</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>979</v>
+        <v>1023</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>980</v>
+        <v>1024</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>981</v>
+        <v>1025</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>982</v>
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1031</v>
       </c>
     </row>
   </sheetData>
@@ -5287,186 +5795,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>983</v>
+        <v>1032</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>984</v>
+        <v>1033</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>985</v>
+        <v>1034</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>986</v>
+        <v>1035</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>987</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>988</v>
+        <v>1037</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>989</v>
+        <v>1038</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>991</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>958</v>
+        <v>1003</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>992</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>948</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>994</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>995</v>
+        <v>1044</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>996</v>
+        <v>1045</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>997</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>998</v>
+        <v>1047</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>999</v>
+        <v>1048</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1000</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1001</v>
+        <v>1050</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1002</v>
+        <v>1051</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1003</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1004</v>
+        <v>1053</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1005</v>
+        <v>1054</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1006</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1007</v>
+        <v>1056</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1008</v>
+        <v>1057</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1009</v>
+        <v>1058</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1010</v>
+        <v>1059</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1011</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1012</v>
+        <v>1061</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1013</v>
+        <v>1062</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1014</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1015</v>
+        <v>1064</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1016</v>
+        <v>1065</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1017</v>
+        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -11008,7 +11516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -11685,6 +12193,241 @@
         <v>69</v>
       </c>
     </row>
+    <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11694,7 +12437,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -11708,7 +12451,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>764</v>
+        <v>798</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>50</v>
@@ -11717,16 +12460,16 @@
         <v>666</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>765</v>
+        <v>799</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>766</v>
+        <v>800</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>767</v>
+        <v>801</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>768</v>
+        <v>802</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11740,10 +12483,10 @@
         <v>679</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="E2" s="2">
-        <v>1718</v>
+        <v>1183</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -11759,10 +12502,10 @@
         <v>693</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="E3" s="2">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -11778,10 +12521,10 @@
         <v>699</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="E4" s="2">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11797,10 +12540,10 @@
         <v>707</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="E5" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -11816,10 +12559,10 @@
         <v>715</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="E6" s="2">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -11835,10 +12578,10 @@
         <v>723</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="E7" s="2">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -11854,10 +12597,10 @@
         <v>730</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="E8" s="2">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -11873,13 +12616,13 @@
         <v>736</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>771</v>
+        <v>805</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -11894,10 +12637,10 @@
         <v>707</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="E10" s="2">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -11913,13 +12656,13 @@
         <v>749</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>771</v>
+        <v>805</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -11934,13 +12677,13 @@
         <v>753</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>771</v>
+        <v>805</v>
       </c>
       <c r="G12" s="2"/>
     </row>
@@ -11955,13 +12698,13 @@
         <v>757</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>771</v>
+        <v>805</v>
       </c>
       <c r="G13" s="2"/>
     </row>
@@ -11976,15 +12719,110 @@
         <v>761</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>771</v>
+        <v>805</v>
       </c>
       <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E15" s="2">
+        <v>82</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E16" s="2">
+        <v>64</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E17" s="2">
+        <v>75</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E18" s="2">
+        <v>73</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E19" s="2">
+        <v>82</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11994,7 +12832,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -12015,143 +12853,47 @@
         <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>772</v>
+        <v>806</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>773</v>
+        <v>807</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>774</v>
+        <v>808</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>775</v>
+        <v>809</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>764</v>
+        <v>798</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>776</v>
+        <v>810</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>777</v>
+        <v>811</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>778</v>
+        <v>812</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>779</v>
+        <v>813</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>780</v>
+        <v>814</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>781</v>
+        <v>815</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>782</v>
+        <v>816</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
+        <v>817</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12161,7 +12903,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -12176,28 +12918,109 @@
         <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>772</v>
+        <v>806</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>774</v>
+        <v>808</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>764</v>
+        <v>798</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>765</v>
+        <v>799</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>803</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>832</v>
       </c>
     </row>
   </sheetData>
@@ -12224,16 +13047,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>804</v>
+        <v>833</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>805</v>
+        <v>834</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>689</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>806</v>
+        <v>835</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -12262,7 +13085,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12285,7 +13108,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12308,7 +13131,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12331,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12354,7 +13177,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12377,7 +13200,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12400,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12423,7 +13246,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12446,7 +13269,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12469,7 +13292,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12492,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12515,7 +13338,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12538,7 +13361,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12561,7 +13384,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12584,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12607,7 +13430,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12630,7 +13453,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12653,7 +13476,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12676,7 +13499,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12699,7 +13522,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12722,7 +13545,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12745,7 +13568,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12768,7 +13591,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>809</v>
+        <v>838</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12791,7 +13614,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12814,7 +13637,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12837,7 +13660,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12860,7 +13683,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12883,7 +13706,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12906,7 +13729,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12929,7 +13752,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12952,7 +13775,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12975,7 +13798,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12998,7 +13821,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13021,7 +13844,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13044,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13067,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13090,7 +13913,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13113,7 +13936,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13136,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13159,7 +13982,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13182,7 +14005,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13205,7 +14028,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13228,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13251,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13274,7 +14097,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13297,7 +14120,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13320,7 +14143,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13343,7 +14166,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13366,7 +14189,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13389,7 +14212,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13412,7 +14235,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13435,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13458,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13481,7 +14304,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13504,7 +14327,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13527,7 +14350,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13550,7 +14373,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13573,7 +14396,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13596,7 +14419,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13619,7 +14442,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13642,7 +14465,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13665,7 +14488,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13688,7 +14511,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13711,7 +14534,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13734,7 +14557,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13757,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13780,7 +14603,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13803,7 +14626,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13826,7 +14649,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13849,7 +14672,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13872,7 +14695,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13895,7 +14718,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13918,7 +14741,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13941,7 +14764,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13964,7 +14787,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13987,7 +14810,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14010,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14033,7 +14856,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14056,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14079,7 +14902,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14102,7 +14925,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14125,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>809</v>
+        <v>838</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14148,7 +14971,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14171,7 +14994,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14194,7 +15017,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14217,7 +15040,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14240,7 +15063,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14263,7 +15086,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14286,7 +15109,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14309,7 +15132,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14332,7 +15155,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14355,7 +15178,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14378,7 +15201,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14401,7 +15224,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14424,7 +15247,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14447,7 +15270,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14470,7 +15293,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14493,7 +15316,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14516,7 +15339,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14539,7 +15362,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>809</v>
+        <v>838</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14562,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14585,7 +15408,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14608,7 +15431,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14631,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>809</v>
+        <v>838</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14654,7 +15477,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14677,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14700,7 +15523,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14723,7 +15546,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>809</v>
+        <v>838</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14746,7 +15569,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14769,7 +15592,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14792,7 +15615,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14815,7 +15638,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14838,7 +15661,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14861,7 +15684,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14884,7 +15707,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14907,7 +15730,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14930,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14953,7 +15776,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14976,7 +15799,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14999,7 +15822,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15010,19 +15833,19 @@
         <v>588</v>
       </c>
       <c r="C122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="2">
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>808</v>
+        <v>836</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15045,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15068,7 +15891,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15091,7 +15914,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15114,7 +15937,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15125,19 +15948,19 @@
         <v>611</v>
       </c>
       <c r="C127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="2">
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>808</v>
+        <v>836</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15160,7 +15983,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15183,7 +16006,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="130" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15206,7 +16029,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="131" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15217,19 +16040,19 @@
         <v>628</v>
       </c>
       <c r="C131" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="2">
         <v>0</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>808</v>
+        <v>836</v>
       </c>
     </row>
     <row r="132" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15252,7 +16075,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="133" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15275,7 +16098,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="134" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15298,7 +16121,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="135" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15309,19 +16132,19 @@
         <v>645</v>
       </c>
       <c r="C135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="2">
         <v>0</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>808</v>
+        <v>836</v>
       </c>
     </row>
     <row r="136" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15344,7 +16167,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="137" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15355,19 +16178,19 @@
         <v>654</v>
       </c>
       <c r="C137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="2">
         <v>0</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>808</v>
+        <v>836</v>
       </c>
     </row>
     <row r="138" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15390,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="139" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15413,7 +16236,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>
@@ -15435,13 +16258,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>810</v>
+        <v>839</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>811</v>
+        <v>840</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>812</v>
+        <v>841</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -15449,212 +16272,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>813</v>
+        <v>842</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>815</v>
+        <v>844</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>816</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>817</v>
+        <v>846</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>818</v>
+        <v>847</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>820</v>
+        <v>849</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>821</v>
+        <v>850</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>822</v>
+        <v>851</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>823</v>
+        <v>852</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>824</v>
+        <v>853</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>825</v>
+        <v>854</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>826</v>
+        <v>855</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>827</v>
+        <v>856</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>828</v>
+        <v>857</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>829</v>
+        <v>858</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>830</v>
+        <v>859</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>816</v>
+        <v>845</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>831</v>
+        <v>860</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>832</v>
+        <v>861</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>692</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>816</v>
+        <v>845</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>833</v>
+        <v>862</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>834</v>
+        <v>863</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>815</v>
+        <v>864</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>816</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>835</v>
+        <v>865</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>836</v>
+        <v>866</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>837</v>
+        <v>867</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>816</v>
+        <v>845</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>838</v>
+        <v>868</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>841</v>
+        <v>871</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>844</v>
+        <v>874</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>845</v>
+        <v>875</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>846</v>
+        <v>876</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>714</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>816</v>
+        <v>845</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-eqe-CYC-4/08-report/CYC-4-cycle-report.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="1065">
   <si>
     <t>Metric</t>
   </si>
@@ -168,7 +168,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) at 2026-10-12T02:10:38.267Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) at 2026-10-12T02:22:34.551Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -2971,7 +2971,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-12T02:10:39.649Z</t>
+    <t>2026-10-12T02:22:36.181Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -2983,7 +2983,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-12T02:10:39.674Z</t>
+    <t>2026-10-12T02:22:36.206Z</t>
   </si>
   <si>
     <t>23 requirements, 5 test cases, 5 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -3238,13 +3238,7 @@
     <t>testing-eqe, traceability-handover</t>
   </si>
   <si>
-    <t>incomplete</t>
-  </si>
-  <si>
-    <t>evidence</t>
-  </si>
-  <si>
-    <t>evidence: missing; results: delivered</t>
+    <t>evidence: delivered; results: delivered</t>
   </si>
   <si>
     <t>Defect agent</t>
@@ -5934,21 +5928,21 @@
         <v>1057</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>1039</v>
@@ -5957,15 +5951,15 @@
         <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>1039</v>
@@ -5974,7 +5968,7 @@
         <v>69</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
   </sheetData>
@@ -12486,7 +12480,7 @@
         <v>803</v>
       </c>
       <c r="E2" s="2">
-        <v>1183</v>
+        <v>1174</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -12505,7 +12499,7 @@
         <v>803</v>
       </c>
       <c r="E3" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -12524,7 +12518,7 @@
         <v>803</v>
       </c>
       <c r="E4" s="2">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -12543,7 +12537,7 @@
         <v>803</v>
       </c>
       <c r="E5" s="2">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -12562,7 +12556,7 @@
         <v>803</v>
       </c>
       <c r="E6" s="2">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -12581,7 +12575,7 @@
         <v>803</v>
       </c>
       <c r="E7" s="2">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -12600,7 +12594,7 @@
         <v>803</v>
       </c>
       <c r="E8" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -12640,7 +12634,7 @@
         <v>803</v>
       </c>
       <c r="E10" s="2">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -12743,7 +12737,7 @@
         <v>803</v>
       </c>
       <c r="E15" s="2">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -12762,7 +12756,7 @@
         <v>803</v>
       </c>
       <c r="E16" s="2">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -12781,7 +12775,7 @@
         <v>803</v>
       </c>
       <c r="E17" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -12800,7 +12794,7 @@
         <v>803</v>
       </c>
       <c r="E18" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -12819,7 +12813,7 @@
         <v>803</v>
       </c>
       <c r="E19" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
